--- a/Data/Excel/world_gather.xlsx
+++ b/Data/Excel/world_gather.xlsx
@@ -236,7 +236,7 @@
         </x:is>
       </x:c>
       <x:c r="B5">
-        <x:v>1001</x:v>
+        <x:v>30400001</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr">
         <x:is>
@@ -244,7 +244,7 @@
         </x:is>
       </x:c>
       <x:c r="D5">
-        <x:v>2001</x:v>
+        <x:v>30902001</x:v>
       </x:c>
       <x:c r="E5">
         <x:v>3</x:v>
@@ -263,7 +263,7 @@
         </x:is>
       </x:c>
       <x:c r="B6">
-        <x:v>1002</x:v>
+        <x:v>30400002</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr">
         <x:is>
@@ -271,7 +271,7 @@
         </x:is>
       </x:c>
       <x:c r="D6">
-        <x:v>2002</x:v>
+        <x:v>30902002</x:v>
       </x:c>
       <x:c r="E6">
         <x:v>3</x:v>
@@ -290,7 +290,7 @@
         </x:is>
       </x:c>
       <x:c r="B7">
-        <x:v>1003</x:v>
+        <x:v>30400003</x:v>
       </x:c>
       <x:c r="C7" t="inlineStr">
         <x:is>
@@ -298,7 +298,7 @@
         </x:is>
       </x:c>
       <x:c r="D7">
-        <x:v>2004</x:v>
+        <x:v>30902004</x:v>
       </x:c>
       <x:c r="E7">
         <x:v>3</x:v>
@@ -317,7 +317,7 @@
         </x:is>
       </x:c>
       <x:c r="B8">
-        <x:v>1004</x:v>
+        <x:v>30400004</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr">
         <x:is>
@@ -325,7 +325,7 @@
         </x:is>
       </x:c>
       <x:c r="D8">
-        <x:v>2005</x:v>
+        <x:v>30902005</x:v>
       </x:c>
       <x:c r="E8">
         <x:v>3</x:v>
@@ -344,7 +344,7 @@
         </x:is>
       </x:c>
       <x:c r="B9">
-        <x:v>1005</x:v>
+        <x:v>30400005</x:v>
       </x:c>
       <x:c r="C9" t="inlineStr">
         <x:is>
@@ -352,7 +352,7 @@
         </x:is>
       </x:c>
       <x:c r="D9">
-        <x:v>2006</x:v>
+        <x:v>30902006</x:v>
       </x:c>
       <x:c r="E9">
         <x:v>2</x:v>
@@ -371,7 +371,7 @@
         </x:is>
       </x:c>
       <x:c r="B10">
-        <x:v>1006</x:v>
+        <x:v>30400006</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr">
         <x:is>
@@ -379,7 +379,7 @@
         </x:is>
       </x:c>
       <x:c r="D10">
-        <x:v>2007</x:v>
+        <x:v>30902007</x:v>
       </x:c>
       <x:c r="E10">
         <x:v>2</x:v>
@@ -398,7 +398,7 @@
         </x:is>
       </x:c>
       <x:c r="B11">
-        <x:v>1007</x:v>
+        <x:v>30400007</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr">
         <x:is>
@@ -406,7 +406,7 @@
         </x:is>
       </x:c>
       <x:c r="D11">
-        <x:v>2008</x:v>
+        <x:v>30902008</x:v>
       </x:c>
       <x:c r="E11">
         <x:v>2</x:v>
